--- a/artfynd/A 32155-2023 artfynd.xlsx
+++ b/artfynd/A 32155-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32155-2023 artfynd.xlsx
+++ b/artfynd/A 32155-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104154124</v>
+        <v>104154195</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>779334.0514876784</v>
+        <v>779298</v>
       </c>
       <c r="R2" t="n">
-        <v>7244192.518421341</v>
+        <v>7244213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104154195</v>
+        <v>104153957</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779297.852004302</v>
+        <v>779611</v>
       </c>
       <c r="R3" t="n">
-        <v>7244213.144869328</v>
+        <v>7244072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104153957</v>
+        <v>104154027</v>
       </c>
       <c r="B4" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779610.5702249735</v>
+        <v>779271</v>
       </c>
       <c r="R4" t="n">
-        <v>7244071.871902778</v>
+        <v>7244195</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104154027</v>
+        <v>104154124</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779270.8754804424</v>
+        <v>779334</v>
       </c>
       <c r="R5" t="n">
-        <v>7244194.537959835</v>
+        <v>7244193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 32155-2023 artfynd.xlsx
+++ b/artfynd/A 32155-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154195</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104153957</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154027</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154124</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>